--- a/master-data-app/src/data/assignment_rules.xlsx
+++ b/master-data-app/src/data/assignment_rules.xlsx
@@ -1,143 +1,422 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\141076\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F95610-83E2-4903-A78F-AF1CFCE4104D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_F1F4019FBFF96A89CA12B051D8002AF6395998B5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7840D872-559F-4DD1-AD8C-CA3FC457C185}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
     <sheet name="Members" sheetId="2" r:id="rId2"/>
     <sheet name="Assignment_Pool" sheetId="3" r:id="rId3"/>
     <sheet name="Notification_Messages" sheetId="4" r:id="rId4"/>
-    <sheet name="Placeholders" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>AXIOM</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Carlito"/>
+          </rPr>
+          <t>Short ID used in Assignment_Pool. Example: MDM001</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Carlito"/>
+          </rPr>
+          <t>Name shown in the confirmation email and the Workbench. Example: Anastasija</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Carlito"/>
+          </rPr>
+          <t>Microsoft 365 / Teams address that receives the message. Example: name@etexgroup.com</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Carlito"/>
+          </rPr>
+          <t>Y = can receive requests. Y = yes, N = no. Example: Y</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Carlito"/>
+          </rPr>
+          <t>Your own comments. The app does not read this column.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>AXIOM</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Carlito"/>
+          </rPr>
+          <t>Company Code. Example: 9320</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Carlito"/>
+          </rPr>
+          <t>Sales Organization. Example: 9321</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Carlito"/>
+          </rPr>
+          <t>Member (from Members) who can receive these requests. Example: MDM001</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Carlito"/>
+          </rPr>
+          <t>Y = this member is in the pool. Y = yes, N = no. Example: Y</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Carlito"/>
+          </rPr>
+          <t>Your own comments. The app does not read this column.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>AXIOM</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Carlito"/>
+          </rPr>
+          <t>Reference of the message, for you. The app does not read it. Example: MSG001</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Carlito"/>
+          </rPr>
+          <t>Y = can be used. Y = yes, N = no. Example: Y</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Carlito"/>
+          </rPr>
+          <t>Teams message text. Use the placeholders below exactly, including the curly brackets. Example: {name}, {request_id} is yours.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="100">
-  <si>
-    <t>Automatic Assignment &amp; Teams Notification Rules</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Editable configuration for fair automatic MDM assignment and randomized Teams messages.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="109">
+  <si>
+    <t>AXIOM · CUSTOMER REQUEST PORTAL</t>
+  </si>
+  <si>
+    <t>Assignment &amp; notification rules</t>
+  </si>
+  <si>
+    <t>Who in the Master Data team receives each request, and the Teams messages they get.</t>
+  </si>
+  <si>
+    <t>The sheets in this file</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>What it controls</t>
   </si>
   <si>
     <t>Members</t>
   </si>
   <si>
-    <t>Add each MDM team member once. Fill in the real Microsoft 365 / Teams email before enabling Teams notification.</t>
+    <t>The Master Data team members who can receive requests.</t>
   </si>
   <si>
     <t>Assignment_Pool</t>
   </si>
   <si>
-    <t>Controls which active members can receive requests for a Company Code + Sales Org.</t>
-  </si>
-  <si>
-    <t>Balancing method</t>
-  </si>
-  <si>
-    <t>The app assigns the new request to the active member with the fewest currently open requests. Ties are randomized.</t>
+    <t>Which members receive requests for each Company Code and Sales Organization.</t>
   </si>
   <si>
     <t>Notification_Messages</t>
   </si>
   <si>
-    <t>Random message templates. Add as many as you like. Use placeholders shown in the sheet.</t>
-  </si>
-  <si>
-    <t>Teams</t>
-  </si>
-  <si>
-    <t>The app will later POST the chosen message + assignee email to a Power Automate / Logic App endpoint.</t>
-  </si>
-  <si>
-    <t>Webhook secret</t>
-  </si>
-  <si>
-    <t>Do NOT put the Power Automate webhook URL in this workbook. Keep it in an app environment variable/secret.</t>
-  </si>
-  <si>
-    <t>Demo route</t>
-  </si>
-  <si>
-    <t>The sample pool is for Company Code 9320 + Sales Org 9321.</t>
-  </si>
-  <si>
-    <t>Editing</t>
-  </si>
-  <si>
-    <t>Set active=Y/N to enable or disable members, pool rows, or message templates.</t>
+    <t>The Teams messages. One is picked at random for each request.</t>
+  </si>
+  <si>
+    <t>How to make a change</t>
+  </si>
+  <si>
+    <t>•  Add a team member: add a row in Members, then add Assignment_Pool rows for their companies.</t>
+  </si>
+  <si>
+    <t>•  Pause someone (holiday): set active to N in their Members or Assignment_Pool rows.</t>
+  </si>
+  <si>
+    <t>•  Add a Teams message: add a row in Notification_Messages using the placeholders below.</t>
+  </si>
+  <si>
+    <t>•  Save the file and refresh the portal; the change is live straight away. Never rename sheets or the column names in row 1.</t>
+  </si>
+  <si>
+    <t>Columns of Members</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>What it means</t>
+  </si>
+  <si>
+    <t>Example</t>
   </si>
   <si>
     <t>member_id</t>
   </si>
   <si>
+    <t>Short ID used in Assignment_Pool.</t>
+  </si>
+  <si>
+    <t>MDM001</t>
+  </si>
+  <si>
     <t>display_name</t>
   </si>
   <si>
+    <t>Name shown in the confirmation email and the Workbench.</t>
+  </si>
+  <si>
+    <t>Anastasija</t>
+  </si>
+  <si>
     <t>email</t>
   </si>
   <si>
+    <t>Microsoft 365 / Teams address that receives the message.</t>
+  </si>
+  <si>
+    <t>name@etexgroup.com</t>
+  </si>
+  <si>
     <t>active</t>
   </si>
   <si>
+    <t>Y = can receive requests. Y = yes, N = no.</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>notes</t>
   </si>
   <si>
-    <t>MDM001</t>
-  </si>
-  <si>
-    <t>Anastasija</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>MDM002</t>
-  </si>
-  <si>
-    <t>Sigita</t>
-  </si>
-  <si>
-    <t>MDM003</t>
-  </si>
-  <si>
-    <t>N</t>
+    <t>Your own comments. The app does not read this column.</t>
+  </si>
+  <si>
+    <t>Columns of Assignment_Pool</t>
   </si>
   <si>
     <t>company_code</t>
   </si>
   <si>
+    <t>Company Code.</t>
+  </si>
+  <si>
+    <t>9320</t>
+  </si>
+  <si>
     <t>sales_org</t>
   </si>
   <si>
-    <t>9320</t>
+    <t>Sales Organization.</t>
   </si>
   <si>
     <t>9321</t>
   </si>
   <si>
+    <t>Member (from Members) who can receive these requests.</t>
+  </si>
+  <si>
+    <t>Y = this member is in the pool. Y = yes, N = no.</t>
+  </si>
+  <si>
+    <t>Columns of Notification_Messages</t>
+  </si>
+  <si>
     <t>message_id</t>
   </si>
   <si>
+    <t>Reference of the message, for you. The app does not read it.</t>
+  </si>
+  <si>
+    <t>MSG001</t>
+  </si>
+  <si>
+    <t>Y = can be used. Y = yes, N = no.</t>
+  </si>
+  <si>
     <t>message_template</t>
   </si>
   <si>
-    <t>MSG001</t>
+    <t>Teams message text. Use the placeholders below exactly, including the curly brackets.</t>
+  </si>
+  <si>
+    <t>{name}, {request_id} is yours.</t>
+  </si>
+  <si>
+    <t>{name}</t>
+  </si>
+  <si>
+    <t>Name of the assigned team member.</t>
+  </si>
+  <si>
+    <t>{request_id}</t>
+  </si>
+  <si>
+    <t>Request number.</t>
+  </si>
+  <si>
+    <t>{customer}</t>
+  </si>
+  <si>
+    <t>Customer name.</t>
+  </si>
+  <si>
+    <t>{customer_id}</t>
+  </si>
+  <si>
+    <t>SAP customer ID.</t>
+  </si>
+  <si>
+    <t>{company_code}</t>
+  </si>
+  <si>
+    <t>{sales_org}</t>
+  </si>
+  <si>
+    <t>{workbench_url}</t>
+  </si>
+  <si>
+    <t>Link that opens the request in the Workbench. If a message leaves it out, the link is added at the end.</t>
+  </si>
+  <si>
+    <t>Good to know</t>
+  </si>
+  <si>
+    <t>•  A request goes to a random active pool member for its Company Code and Sales Organization. Without pool rows for that combination, any active member can receive it.</t>
+  </si>
+  <si>
+    <t>•  A placeholder the app does not know (a typo in the curly brackets) stops the notification. The request is still saved.</t>
+  </si>
+  <si>
+    <t>•  Y, YES, TRUE, 1 and X all count as yes. Set active to N instead of deleting rows.</t>
+  </si>
+  <si>
+    <t>•  Hover over a column name in row 1 of a sheet to see what it means.</t>
+  </si>
+  <si>
+    <t>anastasija.lebedeva@etexgroup.com</t>
   </si>
   <si>
     <t>🎯 {name}, the MDM roulette has spoken: {request_id} is yours. Customer: {customer}.</t>
@@ -255,101 +534,15 @@
   </si>
   <si>
     <t>🍪 No cookie attached, unfortunately. But {name}, you did get {request_id}.</t>
-  </si>
-  <si>
-    <t>Placeholder</t>
-  </si>
-  <si>
-    <t>Meaning</t>
-  </si>
-  <si>
-    <t>{name}</t>
-  </si>
-  <si>
-    <t>Assigned MDM member display name</t>
-  </si>
-  <si>
-    <t>{request_id}</t>
-  </si>
-  <si>
-    <t>Generated request ID</t>
-  </si>
-  <si>
-    <t>{customer}</t>
-  </si>
-  <si>
-    <t>Customer name</t>
-  </si>
-  <si>
-    <t>{customer_id}</t>
-  </si>
-  <si>
-    <t>SAP Customer ID</t>
-  </si>
-  <si>
-    <t>{company_code}</t>
-  </si>
-  <si>
-    <t>Company Code</t>
-  </si>
-  <si>
-    <t>{sales_org}</t>
-  </si>
-  <si>
-    <t>Sales Organization</t>
-  </si>
-  <si>
-    <t>{workbench_url}</t>
-  </si>
-  <si>
-    <t>Customer Master Workbench link if configured</t>
-  </si>
-  <si>
-    <t>sigita.grockiene@etexgroup.com</t>
-  </si>
-  <si>
-    <t>anastasija.lebedeva@etexgroup.com</t>
-  </si>
-  <si>
-    <t>Laura</t>
-  </si>
-  <si>
-    <t>laura.valuckiene@etexgroup.com</t>
-  </si>
-  <si>
-    <t>MDM004</t>
-  </si>
-  <si>
-    <t>Karolina</t>
-  </si>
-  <si>
-    <t>karolina.lozovske@etexgroup.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <sz val="11"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
     <font>
@@ -359,8 +552,49 @@
       <name val="Carlito"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Carlito"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF182033"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF663BFF"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF182033"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667085"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF663BFF"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF182033"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667085"/>
+      <name val="Segoe UI"/>
     </font>
   </fonts>
   <fills count="4">
@@ -372,16 +606,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
+        <fgColor rgb="FF182033"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAF7"/>
+        <fgColor rgb="FFF3EFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -389,32 +623,122 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE4E7EC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE4E7EC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE4E7EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE4E7EC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF663BFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hipersaitas" xfId="1" builtinId="8"/>
+    <cellStyle name="Įprastas" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF667085"/>
+        <name val="Segoe UI"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF2E7D32"/>
+        <name val="Segoe UI"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF667085"/>
+        <name val="Segoe UI"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF2E7D32"/>
+        <name val="Segoe UI"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF667085"/>
+        <name val="Segoe UI"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF2E7D32"/>
+        <name val="Segoe UI"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -428,7 +752,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MembersTable" displayName="MembersTable" ref="A1:E5" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MembersTable" displayName="MembersTable" ref="A1:E2" totalsRowShown="0">
+  <autoFilter ref="A1:E2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="member_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="display_name"/>
@@ -436,12 +761,13 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="active"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="notes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AssignmentPoolTable" displayName="AssignmentPoolTable" ref="A1:E4" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AssignmentPoolTable" displayName="AssignmentPoolTable" ref="A1:E2" totalsRowShown="0">
+  <autoFilter ref="A1:E2" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="company_code"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="sales_org"/>
@@ -449,28 +775,19 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="active"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="notes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="NotificationMessagesTable" displayName="NotificationMessagesTable" ref="A1:C21" totalsRowShown="0">
+  <autoFilter ref="A1:C21" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="message_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="active"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="message_template"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="PlaceholdersTable" displayName="PlaceholdersTable" ref="A1:B8" totalsRowShown="0">
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Placeholder"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Meaning"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -669,98 +986,420 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetPr>
+    <tabColor rgb="FF663BFF"/>
+  </sheetPr>
+  <dimension ref="B2:D51"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="82" customWidth="1"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="78" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20.25">
-      <c r="A1" s="6" t="s">
+    <row r="2" spans="2:4">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="3" spans="1:4" ht="15">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="3" spans="2:4" ht="30" customHeight="1">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+    </row>
+    <row r="4" spans="2:4" ht="32.1" customHeight="1">
+      <c r="B4" s="14" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="29.25">
-      <c r="A4" s="1" t="s">
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="15">
-      <c r="A5" s="1" t="s">
+      <c r="C7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="2:4" ht="15" customHeight="1">
+      <c r="B8" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="29.25">
-      <c r="A6" s="1" t="s">
+      <c r="C8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D8" s="7"/>
+    </row>
+    <row r="9" spans="2:4" ht="15" customHeight="1">
+      <c r="B9" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15">
-      <c r="A7" s="1" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D9" s="7"/>
+    </row>
+    <row r="10" spans="2:4" ht="15" customHeight="1">
+      <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="29.25">
-      <c r="A8" s="1" t="s">
+      <c r="C10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D10" s="7"/>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="29.25">
-      <c r="A9" s="1" t="s">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="2:4" ht="15" customHeight="1">
+      <c r="B13" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+    </row>
+    <row r="14" spans="2:4" ht="15" customHeight="1">
+      <c r="B14" s="12" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="15">
-      <c r="A10" s="1" t="s">
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+    </row>
+    <row r="15" spans="2:4" ht="15" customHeight="1">
+      <c r="B15" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" s="12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15">
-      <c r="A11" s="1" t="s">
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="C19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="15" customHeight="1">
+      <c r="B20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="15" customHeight="1">
+      <c r="B21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="15" customHeight="1">
+      <c r="B22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="15" customHeight="1">
+      <c r="B23" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="15" customHeight="1">
+      <c r="B24" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="15" customHeight="1">
+      <c r="B28" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="15" customHeight="1">
+      <c r="B29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="15" customHeight="1">
+      <c r="B30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" ht="15" customHeight="1">
+      <c r="B31" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="15" customHeight="1">
+      <c r="B32" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" ht="15" customHeight="1">
+      <c r="B36" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" ht="15" customHeight="1">
+      <c r="B37" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="30" customHeight="1">
+      <c r="B38" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" ht="15" customHeight="1">
+      <c r="B39" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" s="7"/>
+    </row>
+    <row r="40" spans="2:4" ht="15" customHeight="1">
+      <c r="B40" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="7"/>
+    </row>
+    <row r="41" spans="2:4" ht="15" customHeight="1">
+      <c r="B41" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" s="7"/>
+    </row>
+    <row r="42" spans="2:4" ht="15" customHeight="1">
+      <c r="B42" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" s="7"/>
+    </row>
+    <row r="43" spans="2:4" ht="15" customHeight="1">
+      <c r="B43" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="7"/>
+    </row>
+    <row r="44" spans="2:4" ht="15" customHeight="1">
+      <c r="B44" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="7"/>
+    </row>
+    <row r="45" spans="2:4" ht="30" customHeight="1">
+      <c r="B45" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D45" s="7"/>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+    </row>
+    <row r="48" spans="2:4" ht="30" customHeight="1">
+      <c r="B48" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+    </row>
+    <row r="49" spans="2:4" ht="15" customHeight="1">
+      <c r="B49" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+    </row>
+    <row r="50" spans="2:4" ht="15" customHeight="1">
+      <c r="B50" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+    </row>
+    <row r="51" spans="2:4" ht="15" customHeight="1">
+      <c r="B51" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="10">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B16:D16"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 Classification: Internal </oddFooter>
   </headerFooter>
@@ -768,536 +1407,414 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF182033"/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="48" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15">
-      <c r="A1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:5" ht="24" customHeight="1">
+      <c r="A1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="B1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B2" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
+      <c r="C2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="D2:D502">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+      <formula>"Y"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+      <formula>"N"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D2:D100" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Check the value" error="Expected one of: Y, N" sqref="D2:D502" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{481EFFA6-75A6-443E-8C39-91B767805117}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{635F237B-6934-4962-BAD4-8960D5461365}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{A7E73D75-C0CD-4E7D-AE34-0C2EF56598FD}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{0E31BB25-3E85-4516-BB67-C00D7349CC47}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
-    <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 Classification: Internal </oddFooter>
+    <oddFooter xml:space="preserve">&amp;C&amp;"Aptos"&amp;11 &amp;K000000_x000D_# Classification: Internal_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 Classification: Internal </oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF182033"/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="48" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="4" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15">
-      <c r="A1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="4" t="s">
+    <row r="1" spans="1:5" ht="24" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
+      <c r="D2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="11"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D2:D502">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"Y"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"N"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D2:D100" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Check the value" error="Expected one of: Y, N" sqref="D2:D502" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
-    <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 Classification: Internal </oddFooter>
+    <oddFooter xml:space="preserve">&amp;C&amp;"Aptos"&amp;11 &amp;K000000_x000D_# Classification: Internal_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 Classification: Internal </oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF182033"/>
+  </sheetPr>
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="90" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15">
-      <c r="A1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>36</v>
+    <row r="1" spans="1:3" ht="24" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>38</v>
+      <c r="A2" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>40</v>
+      <c r="A3" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>42</v>
+      <c r="A4" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>44</v>
+      <c r="A5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>46</v>
+      <c r="A6" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>48</v>
+      <c r="A7" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>50</v>
+      <c r="A8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>52</v>
+      <c r="A9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>54</v>
+      <c r="A10" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>56</v>
+      <c r="A11" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>58</v>
+      <c r="A12" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>60</v>
+      <c r="A13" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>62</v>
+      <c r="A14" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>64</v>
+      <c r="A15" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>66</v>
+      <c r="A16" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>68</v>
+      <c r="A17" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>70</v>
+      <c r="A18" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>72</v>
+      <c r="A19" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>74</v>
+      <c r="A20" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>76</v>
+      <c r="A21" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B521">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Y"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"N"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B2:B200" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Check the value" error="Expected one of: Y, N" sqref="B2:B521" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
-    <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 Classification: Internal </oddFooter>
+    <oddFooter xml:space="preserve">&amp;C&amp;"Aptos"&amp;11 &amp;K000000_x000D_# Classification: Internal_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 Classification: Internal </oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="56" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="15">
-      <c r="A1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 Classification: Internal </oddFooter>
-  </headerFooter>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1578,19 +2095,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33B1BCAB-3D98-42C8-B9A4-8703480207AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{861D8292-01E9-4C71-B126-EC9F96940212}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8FD3DF6-06E8-42CD-8717-5C65208A67D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AD37B5A-FA9A-4EB6-98F6-303EDC762ADA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBECD9FA-2421-484D-BE0E-FA7C14AA6F60}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F75BCF1-536B-4815-935F-AF0E0B5CE643}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{7ceddd7c-561a-4808-b4c3-1692a3515f20}" enabled="1" method="Standard" siteId="{e23c7299-f64d-4de4-a6a1-b40d3145528c}" contentBits="2" removed="0"/>
+  <clbl:label id="{7ceddd7c-561a-4808-b4c3-1692a3515f20}" enabled="1" method="Standard" siteId="{e23c7299-f64d-4de4-a6a1-b40d3145528c}" removed="0"/>
 </clbl:labelList>
 </file>